--- a/reports/Debug-snowbowl-20260106/Month to Date (Actual)_Budget.xlsx
+++ b/reports/Debug-snowbowl-20260106/Month to Date (Actual)_Budget.xlsx
@@ -19,6 +19,15 @@
     <t>Department</t>
   </si>
   <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
     <t>D1010</t>
   </si>
   <si>
@@ -37,6 +46,21 @@
     <t>D8060</t>
   </si>
   <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D4031</t>
+  </si>
+  <si>
+    <t>D4034</t>
+  </si>
+  <si>
+    <t>D5113</t>
+  </si>
+  <si>
+    <t>D6740</t>
+  </si>
+  <si>
     <t>99150</t>
   </si>
   <si>
@@ -58,6 +82,51 @@
     <t>D8040</t>
   </si>
   <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>D4032</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>99100</t>
+  </si>
+  <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>D6030</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
+    <t>D3050</t>
+  </si>
+  <si>
+    <t>D5110</t>
+  </si>
+  <si>
+    <t>D5112</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
     <t>99200</t>
   </si>
   <si>
@@ -67,75 +136,6 @@
     <t>D8050</t>
   </si>
   <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>D4032</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D4031</t>
-  </si>
-  <si>
-    <t>D4034</t>
-  </si>
-  <si>
-    <t>D5113</t>
-  </si>
-  <si>
-    <t>D6740</t>
-  </si>
-  <si>
-    <t>99100</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>D6030</t>
-  </si>
-  <si>
-    <t>D7010</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>D3050</t>
-  </si>
-  <si>
-    <t>D5110</t>
-  </si>
-  <si>
-    <t>D5112</t>
-  </si>
-  <si>
-    <t>D6780</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -154,6 +154,15 @@
     <t>DepartmentTitle</t>
   </si>
   <si>
+    <t>Lift Maintenance</t>
+  </si>
+  <si>
+    <t>Trail Maintenance</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
     <t>Lift Operations</t>
   </si>
   <si>
@@ -172,6 +181,21 @@
     <t>IT Services</t>
   </si>
   <si>
+    <t>Snowmaking</t>
+  </si>
+  <si>
+    <t>Agassiz Retail</t>
+  </si>
+  <si>
+    <t>Fort Valley Lodge</t>
+  </si>
+  <si>
+    <t>Fremont Restaurant</t>
+  </si>
+  <si>
+    <t>Janitorial</t>
+  </si>
+  <si>
     <t>Comp Tickets</t>
   </si>
   <si>
@@ -193,6 +217,51 @@
     <t>HR</t>
   </si>
   <si>
+    <t>Mountain G&amp;A</t>
+  </si>
+  <si>
+    <t>Hart Prairie Retail</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Daily Winter Ticketed</t>
+  </si>
+  <si>
+    <t>Ski School</t>
+  </si>
+  <si>
+    <t>Rentals</t>
+  </si>
+  <si>
+    <t>Base Camp Hotel</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
+    <t>Rental Repair Shop</t>
+  </si>
+  <si>
+    <t>Agassiz Restaurant</t>
+  </si>
+  <si>
+    <t>Base Camp Restaurant</t>
+  </si>
+  <si>
+    <t>Grounds Maintenance</t>
+  </si>
+  <si>
     <t>Winter Season Pass Visits  - Home Resort</t>
   </si>
   <si>
@@ -200,75 +269,6 @@
   </si>
   <si>
     <t>Risk Management</t>
-  </si>
-  <si>
-    <t>Mountain G&amp;A</t>
-  </si>
-  <si>
-    <t>Hart Prairie Retail</t>
-  </si>
-  <si>
-    <t>Resort Services G&amp;A</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Snowmaking</t>
-  </si>
-  <si>
-    <t>Agassiz Retail</t>
-  </si>
-  <si>
-    <t>Fort Valley Lodge</t>
-  </si>
-  <si>
-    <t>Fremont Restaurant</t>
-  </si>
-  <si>
-    <t>Janitorial</t>
-  </si>
-  <si>
-    <t>Daily Winter Ticketed</t>
-  </si>
-  <si>
-    <t>Ski School</t>
-  </si>
-  <si>
-    <t>Rentals</t>
-  </si>
-  <si>
-    <t>Base Camp Hotel</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>Accounting</t>
-  </si>
-  <si>
-    <t>Lift Maintenance</t>
-  </si>
-  <si>
-    <t>Trail Maintenance</t>
-  </si>
-  <si>
-    <t>Housekeeping</t>
-  </si>
-  <si>
-    <t>Rental Repair Shop</t>
-  </si>
-  <si>
-    <t>Agassiz Restaurant</t>
-  </si>
-  <si>
-    <t>Base Camp Restaurant</t>
-  </si>
-  <si>
-    <t>Grounds Maintenance</t>
   </si>
 </sst>
 </file>
@@ -662,7 +662,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="2">
-        <v>34816.66</v>
+        <v>7906.53</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>46</v>
@@ -676,7 +676,7 @@
         <v>41</v>
       </c>
       <c r="C3" s="2">
-        <v>4723.57</v>
+        <v>8463.69</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>47</v>
@@ -690,7 +690,7 @@
         <v>41</v>
       </c>
       <c r="C4" s="2">
-        <v>19136.32</v>
+        <v>2296.90</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>48</v>
@@ -704,7 +704,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="2">
-        <v>15424.71</v>
+        <v>34816.66</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>49</v>
@@ -712,44 +712,44 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2">
-        <v>1135196.00</v>
+        <v>4723.57</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C7" s="2">
-        <v>4379.03</v>
+        <v>19136.32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="2">
-        <v>4267.26</v>
+        <v>15424.71</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -757,10 +757,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" s="2">
-        <v>1850.00</v>
+        <v>1135196.00</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>52</v>
@@ -774,7 +774,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="2">
-        <v>3825.00</v>
+        <v>4379.03</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>53</v>
@@ -788,7 +788,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="2">
-        <v>5482.26</v>
+        <v>4267.26</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>54</v>
@@ -802,7 +802,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="2">
-        <v>4415.10</v>
+        <v>13165.68</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>55</v>
@@ -813,10 +813,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2">
-        <v>3580.44</v>
+        <v>6645.82</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>56</v>
@@ -827,10 +827,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2">
-        <v>0.00</v>
+        <v>1092.96</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>56</v>
@@ -841,10 +841,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2">
-        <v>5080.68</v>
+        <v>1620.36</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>57</v>
@@ -852,100 +852,100 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C16" s="2">
-        <v>2885.24</v>
+        <v>1873.34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2">
-        <v>5550.00</v>
+        <v>4228.36</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="2">
-        <v>15402.61</v>
+        <v>23060.91</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="2">
-        <v>126096.87</v>
+        <v>5534.11</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C20" s="2">
-        <v>866.28</v>
+        <v>1850.00</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="2">
-        <v>5470.32</v>
+        <v>3825.00</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="2">
-        <v>3249.54</v>
+        <v>5482.26</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -953,10 +953,10 @@
         <v>18</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="2">
-        <v>101769.56</v>
+        <v>4415.10</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>63</v>
@@ -970,7 +970,7 @@
         <v>41</v>
       </c>
       <c r="C24" s="2">
-        <v>1500.36</v>
+        <v>3580.44</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>64</v>
@@ -978,58 +978,58 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" s="2">
-        <v>2907.29</v>
+        <v>0.00</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C26" s="2">
-        <v>3598.56</v>
+        <v>5080.68</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C27" s="2">
-        <v>13165.68</v>
+        <v>2885.24</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="2">
-        <v>6645.82</v>
+        <v>5470.32</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1040,7 +1040,7 @@
         <v>41</v>
       </c>
       <c r="C29" s="2">
-        <v>1092.96</v>
+        <v>3249.54</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>68</v>
@@ -1048,16 +1048,16 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="2">
-        <v>1620.36</v>
+        <v>101769.56</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1068,7 +1068,7 @@
         <v>41</v>
       </c>
       <c r="C31" s="2">
-        <v>1873.34</v>
+        <v>1500.36</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>69</v>
@@ -1082,7 +1082,7 @@
         <v>41</v>
       </c>
       <c r="C32" s="2">
-        <v>4228.36</v>
+        <v>2907.29</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>70</v>
@@ -1090,44 +1090,44 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="2">
-        <v>23060.91</v>
+        <v>3598.56</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C34" s="2">
-        <v>5534.11</v>
+        <v>9900.00</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C35" s="2">
-        <v>9900.00</v>
+        <v>31183.69</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1135,10 +1135,10 @@
         <v>28</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C36" s="2">
-        <v>31183.69</v>
+        <v>125097.00</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>73</v>
@@ -1146,16 +1146,16 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C37" s="2">
-        <v>125097.00</v>
+        <v>258083.00</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1163,10 +1163,10 @@
         <v>29</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="2">
-        <v>258083.00</v>
+        <v>16514.16</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>74</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C39" s="2">
-        <v>16514.16</v>
+        <v>3440.24</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1191,10 +1191,10 @@
         <v>30</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C40" s="2">
-        <v>3440.24</v>
+        <v>23779.01</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>75</v>
@@ -1202,44 +1202,44 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="2">
-        <v>23779.01</v>
+        <v>3246.30</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C42" s="2">
-        <v>3246.30</v>
+        <v>5201.46</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C43" s="2">
-        <v>5201.46</v>
+        <v>1985.00</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1247,10 +1247,10 @@
         <v>33</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C44" s="2">
-        <v>7906.53</v>
+        <v>6302.00</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>78</v>
@@ -1264,7 +1264,7 @@
         <v>41</v>
       </c>
       <c r="C45" s="2">
-        <v>8463.69</v>
+        <v>6912.04</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>79</v>
@@ -1272,58 +1272,58 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C46" s="2">
-        <v>2296.90</v>
+        <v>66016.80</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C47" s="2">
-        <v>1985.00</v>
+        <v>2490.77</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C48" s="2">
-        <v>6302.00</v>
+        <v>6554.52</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C49" s="2">
-        <v>6912.04</v>
+        <v>1931.78</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1331,10 +1331,10 @@
         <v>37</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C50" s="2">
-        <v>66016.80</v>
+        <v>5550.00</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>82</v>
@@ -1348,7 +1348,7 @@
         <v>41</v>
       </c>
       <c r="C51" s="2">
-        <v>2490.77</v>
+        <v>15402.61</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>83</v>
@@ -1362,7 +1362,7 @@
         <v>42</v>
       </c>
       <c r="C52" s="2">
-        <v>6554.52</v>
+        <v>126096.87</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>83</v>
@@ -1376,7 +1376,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="2">
-        <v>1931.78</v>
+        <v>866.28</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>84</v>
